--- a/Config.xlsx
+++ b/Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andrei\Documents\GitHub\Trip-Planner-Bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A83FEA81-DBBA-476E-BF7B-10F99D943BBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86689E3-B96D-4DD2-9DEB-1ACAD9C8A3FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3000" yWindow="3000" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23868" yWindow="2448" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
     <t>EmailDestinatar</t>
   </si>
   <si>
-    <t>mail_exemplu@gmail.com</t>
+    <t>andreiionescu441@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -366,12 +366,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="24.26953125" customWidth="1"/>
+    <col min="1" max="2" width="24.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -379,7 +379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
